--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-code-a-barres.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-code-a-barres.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2341" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2355" uniqueCount="291">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -454,6 +454,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -643,6 +646,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -653,10 +659,25 @@
     <t>Bloc narratif de la section</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -669,6 +690,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -676,6 +706,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -683,6 +716,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -836,6 +872,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1212,7 +1254,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -3015,7 +3057,9 @@
       <c r="K18" t="s" s="2">
         <v>141</v>
       </c>
-      <c r="L18" s="2"/>
+      <c r="L18" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3086,10 +3130,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3123,7 +3167,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>74</v>
@@ -3145,7 +3189,7 @@
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>74</v>
@@ -3163,7 +3207,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3183,10 +3227,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3220,7 +3264,7 @@
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>74</v>
@@ -3242,7 +3286,7 @@
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -3260,7 +3304,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3280,10 +3324,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3297,7 +3341,7 @@
         <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>74</v>
@@ -3309,10 +3353,10 @@
         <v>95</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3363,7 +3407,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3383,10 +3427,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3400,7 +3444,7 @@
         <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>74</v>
@@ -3409,13 +3453,13 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3466,7 +3510,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3486,10 +3530,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3587,10 +3631,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3619,7 +3663,7 @@
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3631,7 +3675,7 @@
         <v>74</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>74</v>
@@ -3670,7 +3714,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3690,17 +3734,17 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>75</v>
@@ -3722,7 +3766,7 @@
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3734,7 +3778,7 @@
         <v>74</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>74</v>
@@ -3773,7 +3817,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3793,17 +3837,17 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -3825,7 +3869,7 @@
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3837,7 +3881,7 @@
         <v>74</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>74</v>
@@ -3876,7 +3920,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3896,17 +3940,17 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>80</v>
@@ -3928,7 +3972,7 @@
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3979,7 +4023,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3999,17 +4043,17 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>75</v>
@@ -4031,7 +4075,7 @@
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4043,7 +4087,7 @@
         <v>74</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>74</v>
@@ -4082,7 +4126,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4102,10 +4146,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4128,11 +4172,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4183,7 +4227,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4203,10 +4247,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4233,7 +4277,7 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4284,7 +4328,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4304,17 +4348,17 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
@@ -4332,11 +4376,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4387,7 +4431,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4407,17 +4451,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4435,11 +4479,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4490,7 +4534,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4510,17 +4554,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4538,11 +4582,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4593,7 +4637,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4613,10 +4657,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4630,7 +4674,7 @@
         <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>74</v>
@@ -4639,16 +4683,18 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+      <c r="O34" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>74</v>
       </c>
@@ -4696,7 +4742,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4716,10 +4762,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4733,7 +4779,7 @@
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -4742,15 +4788,17 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>74</v>
@@ -4799,7 +4847,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4819,10 +4867,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4845,12 +4893,16 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="L36" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>74</v>
       </c>
@@ -4898,7 +4950,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4918,10 +4970,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4946,10 +4998,14 @@
       <c r="K37" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L37" s="2"/>
+      <c r="L37" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>74</v>
       </c>
@@ -4977,7 +5033,7 @@
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>74</v>
@@ -4995,7 +5051,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5015,10 +5071,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5041,12 +5097,18 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="L38" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+      <c r="N38" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>74</v>
       </c>
@@ -5094,7 +5156,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5114,10 +5176,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5140,12 +5202,14 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>74</v>
       </c>
@@ -5193,7 +5257,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5213,10 +5277,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5239,12 +5303,14 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>74</v>
       </c>
@@ -5292,7 +5358,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5312,10 +5378,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5329,7 +5395,7 @@
         <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5338,10 +5404,10 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
@@ -5393,7 +5459,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5413,10 +5479,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5514,10 +5580,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5615,10 +5681,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5716,10 +5782,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5817,10 +5883,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5920,10 +5986,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6023,10 +6089,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6126,10 +6192,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6229,10 +6295,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6330,10 +6396,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6347,7 +6413,7 @@
         <v>75</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>74</v>
@@ -6363,14 +6429,14 @@
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="Q51" s="2"/>
       <c r="R51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>74</v>
@@ -6389,7 +6455,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>74</v>
@@ -6407,7 +6473,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6427,10 +6493,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6464,7 +6530,7 @@
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>74</v>
@@ -6506,7 +6572,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6526,10 +6592,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6552,7 +6618,7 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
@@ -6605,7 +6671,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6625,10 +6691,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6651,7 +6717,7 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
@@ -6704,7 +6770,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6724,10 +6790,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6750,7 +6816,7 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
@@ -6803,7 +6869,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6823,10 +6889,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6849,7 +6915,7 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
@@ -6902,7 +6968,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -6922,10 +6988,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6948,7 +7014,7 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -7001,7 +7067,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7021,10 +7087,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7047,7 +7113,7 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -7100,7 +7166,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7120,10 +7186,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7146,7 +7212,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7199,7 +7265,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7219,10 +7285,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7245,7 +7311,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7298,7 +7364,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7318,10 +7384,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7344,7 +7410,7 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7397,7 +7463,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7417,10 +7483,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7443,12 +7509,16 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="L62" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>276</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>74</v>
       </c>
@@ -7496,7 +7566,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7516,10 +7586,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7617,10 +7687,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7718,10 +7788,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7819,10 +7889,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -7920,10 +7990,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8023,10 +8093,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8126,10 +8196,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8229,10 +8299,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8332,10 +8402,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8433,10 +8503,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8463,7 +8533,7 @@
       </c>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8472,7 +8542,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>74</v>
@@ -8514,7 +8584,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8534,10 +8604,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8571,7 +8641,7 @@
       </c>
       <c r="Q73" s="2"/>
       <c r="R73" t="s" s="2">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="S73" t="s" s="2">
         <v>74</v>
@@ -8613,7 +8683,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8633,10 +8703,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8659,7 +8729,7 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
@@ -8712,7 +8782,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>
